--- a/data/trans_camb/P1412-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1412-Edad-trans_camb.xlsx
@@ -641,17 +641,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,32</t>
+          <t>-0,41; 1,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,0</t>
+          <t>-1,16; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,63</t>
+          <t>-0,11; 0,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,15</t>
+          <t>-0,15; 1,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,0</t>
+          <t>-0,77; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -807,12 +807,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,62</t>
+          <t>-0,08; 0,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,32; 0,0</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,29</t>
+          <t>-0,48; 0,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,27</t>
+          <t>-0,51; 0,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-15,24%</t>
+          <t>-19,69%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>102,14%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,37</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,0</t>
+          <t>-1,21; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,22</t>
+          <t>-0,25; 1,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,76</t>
+          <t>0,08; 0,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,0</t>
+          <t>-0,56; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 0,83</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>143,67%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>177,47%</t>
+          <t>219,98%</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-86,57; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,49; —</t>
+          <t>-53,95; —</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,56</t>
+          <t>0,5</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,17</t>
+          <t>0,42; 3,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,57</t>
+          <t>-0,19; 1,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,97</t>
+          <t>-1,37; 0,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,95</t>
+          <t>-1,17; 1,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,71</t>
+          <t>-0,13; 1,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,92</t>
+          <t>-0,48; 0,95</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>233,63%</t>
+          <t>207,66%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>50,15%</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-70,72; 353,16</t>
+          <t>-67,36; 402,88</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 669,61</t>
+          <t>-32,98; 600,02</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,27; 393,0</t>
+          <t>-49,57; 474,75</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-0,15</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>-0,01</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 2,16</t>
+          <t>-3,81; 2,12</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,74</t>
+          <t>-3,31; 1,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,19</t>
+          <t>-0,86; 2,21</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,83</t>
+          <t>-1,12; 1,29</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,65</t>
+          <t>-1,37; 1,65</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,84</t>
+          <t>-1,54; 1,13</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-9,82%</t>
+          <t>-14,31%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-18,23%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-21,29%</t>
+          <t>-0,4%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-75,66; 170,94</t>
+          <t>-79,43; 153,21</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-68,86; 141,43</t>
+          <t>-68,31; 149,61</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-80,48; —</t>
+          <t>-80,68; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-82,97; inf</t>
+          <t>-68,18; 545,0</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-57,71; 172,62</t>
+          <t>-55,56; 180,0</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-70,52; 98,36</t>
+          <t>-55,06; 128,82</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-0,61</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-2,62</t>
+          <t>-2,51</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-1,64</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 1,5</t>
+          <t>-4,55; 1,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,28</t>
+          <t>-3,54; 2,5</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 0,22</t>
+          <t>-4,83; 0,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -0,48</t>
+          <t>-4,93; -0,46</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 0,11</t>
+          <t>-3,75; 0,14</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,86; -0,13</t>
+          <t>-3,67; 0,0</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-14,61%</t>
+          <t>-8,64%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-64,99%</t>
+          <t>-62,2%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-44,48%</t>
+          <t>-40,32%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-78,41; 75,63</t>
+          <t>-74,01; 74,19</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-60,27; 121,42</t>
+          <t>-56,51; 108,47</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-84,75; 23,57</t>
+          <t>-85,34; 19,58</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-84,26; -17,57</t>
+          <t>-81,99; -14,04</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-74,71; 8,0</t>
+          <t>-73,22; 7,81</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-68,1; -3,39</t>
+          <t>-66,14; 0,08</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-0,01</t>
+          <t>0,06</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,5</t>
+          <t>-0,32; 0,54</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,61</t>
+          <t>-0,15; 0,72</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,23</t>
+          <t>-0,54; 0,2</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,13</t>
+          <t>-0,51; 0,19</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,24</t>
+          <t>-0,32; 0,23</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,26</t>
+          <t>-0,2; 0,33</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-29,68%</t>
+          <t>-19,37%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-1,16%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-39,03; 116,14</t>
+          <t>-37,33; 130,17</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 136,02</t>
+          <t>-19,31; 157,99</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-60,64; 51,07</t>
+          <t>-60,97; 45,79</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-61,49; 27,17</t>
+          <t>-53,77; 45,03</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-38,6; 46,1</t>
+          <t>-39,97; 42,5</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 51,74</t>
+          <t>-23,51; 67,19</t>
         </is>
       </c>
     </row>
